--- a/src/analyses/linear_regression/AgonismTo.xlsx
+++ b/src/analyses/linear_regression/AgonismTo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,16 +477,16 @@
         <v>45195</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_011_Unit 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(700.0, 1000.0)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,11 +496,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.3014322029369254</v>
+        <v>0.3154409906494819</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +511,16 @@
         <v>45195</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_011_Unit 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(700.0, 1000.0)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -530,11 +530,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.3319756904937733</v>
+        <v>0.2621399188400637</v>
       </c>
     </row>
     <row r="4">
@@ -545,16 +545,16 @@
         <v>45195</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_011_Unit 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(700.0, 1000.0)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3005539773660508</v>
+        <v>0.3226238342930274</v>
       </c>
     </row>
     <row r="5">
@@ -579,16 +579,16 @@
         <v>45195</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_020</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(50.0, 150.0)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -598,11 +598,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.3162297823038918</v>
+        <v>0.3075051229508194</v>
       </c>
     </row>
     <row r="6">
@@ -613,16 +613,16 @@
         <v>45195</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_007_Unit 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(100.0, 200.0)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -632,11 +632,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.2887803909777151</v>
+        <v>0.4912031144718124</v>
       </c>
     </row>
     <row r="7">
@@ -647,16 +647,16 @@
         <v>45195</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_007_Unit 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(100.0, 200.0)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.4040581760294064</v>
+        <v>0.3843444853529694</v>
       </c>
     </row>
     <row r="8">
@@ -681,16 +681,16 @@
         <v>45195</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_007_Unit 2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(100.0, 200.0)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -700,11 +700,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.4283440228402101</v>
+        <v>0.4301297359305357</v>
       </c>
     </row>
     <row r="9">
@@ -715,16 +715,16 @@
         <v>45195</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_027_Unit 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(150.0, 350.0)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -734,11 +734,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.3075051229508194</v>
+        <v>0.3416793287132939</v>
       </c>
     </row>
     <row r="10">
@@ -746,19 +746,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45202</v>
+        <v>45195</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(200.0, 400.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -768,11 +768,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.6337580897233983</v>
+        <v>0.2504707572985375</v>
       </c>
     </row>
     <row r="11">
@@ -780,19 +780,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45202</v>
+        <v>45195</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(200.0, 400.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -802,11 +802,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.2830638671731048</v>
+        <v>0.6956880948803782</v>
       </c>
     </row>
     <row r="12">
@@ -814,19 +814,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45202</v>
+        <v>45195</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -836,11 +836,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.2552186888052754</v>
+        <v>0.3848395975898196</v>
       </c>
     </row>
     <row r="13">
@@ -851,16 +851,16 @@
         <v>45202</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -870,11 +870,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4741712087207437</v>
+        <v>0.2556528598009871</v>
       </c>
     </row>
     <row r="14">
@@ -885,16 +885,16 @@
         <v>45202</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Channel.C_025</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(1400.0, 1550.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,11 +904,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.4308835357561923</v>
+        <v>0.2719885920560027</v>
       </c>
     </row>
     <row r="15">
@@ -919,16 +919,16 @@
         <v>45202</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Channel.C_025</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(1400.0, 1550.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -938,11 +938,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.5146113101793981</v>
+        <v>0.2519157305788771</v>
       </c>
     </row>
     <row r="16">
@@ -953,16 +953,16 @@
         <v>45202</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Channel.C_025</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(1400.0, 1550.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.2642533099688473</v>
+        <v>0.4395443580963553</v>
       </c>
     </row>
     <row r="17">
@@ -987,16 +987,16 @@
         <v>45202</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Channel.C_010_Unit 2</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1006,11 +1006,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.6372247816344065</v>
+        <v>0.2779914566644892</v>
       </c>
     </row>
     <row r="18">
@@ -1021,16 +1021,16 @@
         <v>45202</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Channel.C_010_Unit 2</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(2150.0, 2250.0)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1040,11 +1040,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.2644743197486034</v>
+        <v>0.2761936996832915</v>
       </c>
     </row>
     <row r="19">
@@ -1052,19 +1052,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_026_Unit 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(1900.0, 2000.0)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1074,11 +1074,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.4220095693779904</v>
+        <v>0.7680999808366953</v>
       </c>
     </row>
     <row r="20">
@@ -1086,19 +1086,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_013_Unit 1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1108,11 +1108,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.626777251184834</v>
+        <v>0.3462509044217922</v>
       </c>
     </row>
     <row r="21">
@@ -1120,19 +1120,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_006</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(1550.0, 1650.0)</t>
+          <t>(450.0, 650.0)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.3711857860177675</v>
+        <v>0.4522808696664382</v>
       </c>
     </row>
     <row r="22">
@@ -1154,19 +1154,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_006</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(1050.0, 1150.0)</t>
+          <t>(450.0, 650.0)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.3861506948899239</v>
+        <v>0.3485297285241373</v>
       </c>
     </row>
     <row r="23">
@@ -1188,19 +1188,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(1050.0, 1150.0)</t>
+          <t>(200.0, 650.0)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1210,11 +1210,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.6855506123951927</v>
+        <v>0.6461718532280538</v>
       </c>
     </row>
     <row r="24">
@@ -1222,19 +1222,19 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(1050.0, 1150.0)</t>
+          <t>(1000.0, 1100.0)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1244,11 +1244,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.4605308276688854</v>
+        <v>0.3399602385685884</v>
       </c>
     </row>
     <row r="25">
@@ -1256,19 +1256,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(1950.0, 2050.0)</t>
+          <t>(1000.0, 1100.0)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1278,11 +1278,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.8663654835663502</v>
+        <v>0.3873278698016951</v>
       </c>
     </row>
     <row r="26">
@@ -1290,19 +1290,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(1950.0, 2050.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.4644575936883629</v>
+        <v>0.6372247816344065</v>
       </c>
     </row>
     <row r="27">
@@ -1324,19 +1324,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.2839212755702717</v>
+        <v>0.2644743197486034</v>
       </c>
     </row>
     <row r="28">
@@ -1358,19 +1358,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.4214242943426267</v>
+        <v>0.2654840579710145</v>
       </c>
     </row>
     <row r="29">
@@ -1392,19 +1392,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Channel.C_013</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.6807084204061078</v>
+        <v>0.3987197282680585</v>
       </c>
     </row>
     <row r="30">
@@ -1426,19 +1426,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Channel.C_013</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(1600.0, 1700.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1448,11 +1448,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.4091938585095537</v>
+        <v>0.2660430586488493</v>
       </c>
     </row>
     <row r="31">
@@ -1460,19 +1460,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_019_Unit 3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1482,11 +1482,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.4818932919844116</v>
+        <v>0.3287525122326942</v>
       </c>
     </row>
     <row r="32">
@@ -1494,19 +1494,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
+          <t>(100.0, 700.0)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.3251812412204463</v>
+        <v>0.2986272314969575</v>
       </c>
     </row>
     <row r="33">
@@ -1528,19 +1528,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
+          <t>(100.0, 700.0)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1550,11 +1550,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.3534795347759113</v>
+        <v>0.2514735055239452</v>
       </c>
     </row>
     <row r="34">
@@ -1562,19 +1562,19 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_019_Unit 3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(200.0, 550.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1584,11 +1584,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.5450073871270649</v>
+        <v>0.2673547565038489</v>
       </c>
     </row>
     <row r="35">
@@ -1596,19 +1596,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_019_Unit 3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(200.0, 550.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1618,11 +1618,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.2692957915344849</v>
+        <v>0.3316177867345523</v>
       </c>
     </row>
     <row r="36">
@@ -1630,19 +1630,19 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(200.0, 550.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1652,11 +1652,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.3741133587590693</v>
+        <v>0.2830002652754444</v>
       </c>
     </row>
     <row r="37">
@@ -1664,19 +1664,19 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.3652133205520296</v>
+        <v>0.3124123545512464</v>
       </c>
     </row>
     <row r="38">
@@ -1698,19 +1698,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_020_Unit 2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1720,11 +1720,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.418862309657889</v>
+        <v>0.2592266205061445</v>
       </c>
     </row>
     <row r="39">
@@ -1732,19 +1732,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_020_Unit 2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1754,11 +1754,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.3553765069507296</v>
+        <v>0.6131236152363444</v>
       </c>
     </row>
     <row r="40">
@@ -1766,19 +1766,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_020_Unit 2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1788,11 +1788,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.5205614776791224</v>
+        <v>0.2627358060694432</v>
       </c>
     </row>
     <row r="41">
@@ -1800,19 +1800,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.2795215205712651</v>
+        <v>0.3680814860246469</v>
       </c>
     </row>
     <row r="42">
@@ -1834,19 +1834,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1856,11 +1856,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.409660941324242</v>
+        <v>0.6312083114314069</v>
       </c>
     </row>
     <row r="43">
@@ -1868,19 +1868,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1890,11 +1890,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.2739757885234303</v>
+        <v>0.3071024715643165</v>
       </c>
     </row>
     <row r="44">
@@ -1902,19 +1902,19 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45252</v>
+        <v>45203</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(1900.0, 2050.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1924,11 +1924,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.4625070845962397</v>
+        <v>0.4071068848907632</v>
       </c>
     </row>
     <row r="45">
@@ -1936,19 +1936,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45252</v>
+        <v>45203</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(1900.0, 2050.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1958,11 +1958,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.401531051964512</v>
+        <v>0.2831257911673597</v>
       </c>
     </row>
     <row r="46">
@@ -1970,19 +1970,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45271</v>
+        <v>45203</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Channel.C_030</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(400.0, 500.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1992,11 +1992,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.37624669388292</v>
+        <v>0.3383573450667826</v>
       </c>
     </row>
     <row r="47">
@@ -2004,19 +2004,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Channel.C_024</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(1400.0, 1550.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.4030975471868115</v>
+        <v>0.319186109615503</v>
       </c>
     </row>
     <row r="48">
@@ -2038,19 +2038,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Channel.C_024</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(1400.0, 1550.0)</t>
+          <t>(100.0, 450.0)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2060,11 +2060,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.6396163259807964</v>
+        <v>0.2967076195487222</v>
       </c>
     </row>
     <row r="49">
@@ -2072,19 +2072,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(100.0, 450.0)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2094,11 +2094,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.415553809897879</v>
+        <v>0.3916439250182306</v>
       </c>
     </row>
     <row r="50">
@@ -2106,19 +2106,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2128,11 +2128,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.4692413793103448</v>
+        <v>0.3602402645057381</v>
       </c>
     </row>
     <row r="51">
@@ -2140,19 +2140,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2162,11 +2162,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.4788334542123145</v>
+        <v>0.5937282326825182</v>
       </c>
     </row>
     <row r="52">
@@ -2174,19 +2174,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45278</v>
+        <v>45203</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Channel.C_029</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2196,11 +2196,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.3840018548574078</v>
+        <v>0.3019501560316625</v>
       </c>
     </row>
     <row r="53">
@@ -2208,19 +2208,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45278</v>
+        <v>45203</v>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Channel.C_029</t>
+          <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2230,11 +2230,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.2804503098245116</v>
+        <v>0.4163913143938898</v>
       </c>
     </row>
     <row r="54">
@@ -2242,19 +2242,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45278</v>
+        <v>45203</v>
       </c>
       <c r="C54" t="n">
         <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Channel.C_029</t>
+          <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2264,11 +2264,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.4166517877639305</v>
+        <v>0.2799484943396999</v>
       </c>
     </row>
     <row r="55">
@@ -2276,19 +2276,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45278</v>
+        <v>45203</v>
       </c>
       <c r="C55" t="n">
         <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Channel.C_029</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.2933507170795306</v>
+        <v>0.2556474069540627</v>
       </c>
     </row>
     <row r="56">
@@ -2310,14 +2310,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45195</v>
+        <v>45203</v>
       </c>
       <c r="C56" t="n">
         <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2332,11 +2332,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.2504707572985375</v>
+        <v>0.2739201316430339</v>
       </c>
     </row>
     <row r="57">
@@ -2344,14 +2344,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45195</v>
+        <v>45203</v>
       </c>
       <c r="C57" t="n">
         <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.6956880948803782</v>
+        <v>0.5844988310964199</v>
       </c>
     </row>
     <row r="58">
@@ -2378,14 +2378,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45195</v>
+        <v>45203</v>
       </c>
       <c r="C58" t="n">
         <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2400,11 +2400,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.3848395975898196</v>
+        <v>0.2653096196922773</v>
       </c>
     </row>
     <row r="59">
@@ -2412,19 +2412,19 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="C59" t="n">
         <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Channel.C_013_Unit 1</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2434,11 +2434,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.3462509044217922</v>
+        <v>0.4484654545430349</v>
       </c>
     </row>
     <row r="60">
@@ -2449,16 +2449,16 @@
         <v>45203</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Channel.C_004_Unit 1</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(0.0, 750.0)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2468,11 +2468,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.2986272314969575</v>
+        <v>0.2809183306350064</v>
       </c>
     </row>
     <row r="61">
@@ -2480,7 +2480,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(1000.0, 1100.0)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2502,11 +2502,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.2514735055239452</v>
+        <v>0.2522052731614601</v>
       </c>
     </row>
     <row r="62">
@@ -2514,19 +2514,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Channel.C_019_Unit 3</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
+          <t>(500.0, 850.0)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2536,11 +2536,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.2673547565038489</v>
+        <v>0.3299663299663299</v>
       </c>
     </row>
     <row r="63">
@@ -2548,19 +2548,19 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Channel.C_019_Unit 3</t>
+          <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
+          <t>(50.0, 350.0)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2570,11 +2570,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.3316177867345523</v>
+        <v>0.4920782851817336</v>
       </c>
     </row>
     <row r="64">
@@ -2582,7 +2582,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C64" t="n">
         <v>2</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
+          <t>(50.0, 350.0)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2604,11 +2604,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.3124123545512464</v>
+        <v>0.5285511074984759</v>
       </c>
     </row>
     <row r="65">
@@ -2616,19 +2616,19 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Channel.C_020_Unit 2</t>
+          <t>Channel.C_019_Unit 2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(2200.0, 2300.0)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2638,11 +2638,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.2592266205061445</v>
+        <v>0.3684210526315789</v>
       </c>
     </row>
     <row r="66">
@@ -2650,19 +2650,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Channel.C_020_Unit 2</t>
+          <t>Channel.C_019_Unit 2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(2200.0, 2300.0)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2672,11 +2672,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.6131236152363444</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="67">
@@ -2684,19 +2684,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45203</v>
+        <v>45208</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Channel.C_020_Unit 2</t>
+          <t>Channel.C_013</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(600.0, 750.0)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2706,11 +2706,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.2627358060694432</v>
+        <v>0.6091617933723198</v>
       </c>
     </row>
     <row r="68">
@@ -2718,19 +2718,19 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45203</v>
+        <v>45208</v>
       </c>
       <c r="C68" t="n">
         <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_013</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(600.0, 750.0)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2740,11 +2740,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.3602402645057381</v>
+        <v>0.5159176164951547</v>
       </c>
     </row>
     <row r="69">
@@ -2752,19 +2752,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_007</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(1150.0, 1250.0)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2774,11 +2774,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.5937282326825182</v>
+        <v>0.8117953491478447</v>
       </c>
     </row>
     <row r="70">
@@ -2786,19 +2786,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_007</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(1150.0, 1250.0)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.3019501560316625</v>
+        <v>0.3900134952766531</v>
       </c>
     </row>
     <row r="71">
@@ -2820,19 +2820,19 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Channel.C_004_Unit 2</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2842,11 +2842,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.4163913143938898</v>
+        <v>0.4725657118001616</v>
       </c>
     </row>
     <row r="72">
@@ -2854,19 +2854,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Channel.C_004_Unit 2</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.2799484943396999</v>
+        <v>0.5227012254253726</v>
       </c>
     </row>
     <row r="73">
@@ -2888,19 +2888,19 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(300.0, 550.0)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2910,11 +2910,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.2556474069540627</v>
+        <v>0.3951980621259618</v>
       </c>
     </row>
     <row r="74">
@@ -2922,19 +2922,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(1550.0, 1650.0)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2944,11 +2944,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.2739201316430339</v>
+        <v>0.4968970483107303</v>
       </c>
     </row>
     <row r="75">
@@ -2956,19 +2956,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(1550.0, 1650.0)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.5844988310964199</v>
+        <v>0.5570526315789474</v>
       </c>
     </row>
     <row r="76">
@@ -2990,19 +2990,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(1550.0, 1650.0)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3012,11 +3012,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.2653096196922773</v>
+        <v>0.798081841432225</v>
       </c>
     </row>
     <row r="77">
@@ -3024,19 +3024,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3046,11 +3046,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.4484654545430349</v>
+        <v>0.2683625858372787</v>
       </c>
     </row>
     <row r="78">
@@ -3058,19 +3058,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Channel.C_022_Unit 2</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.2809183306350064</v>
+        <v>0.3182732477177781</v>
       </c>
     </row>
     <row r="79">
@@ -3092,19 +3092,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45223</v>
+        <v>45210</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_013</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(1650.0, 1800.0)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.3806914464845498</v>
+        <v>0.5220690596788919</v>
       </c>
     </row>
     <row r="80">
@@ -3126,10 +3126,10 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45223</v>
+        <v>45210</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3148,11 +3148,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.251227808839487</v>
+        <v>0.2839212755702717</v>
       </c>
     </row>
     <row r="81">
@@ -3160,10 +3160,10 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45223</v>
+        <v>45210</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3182,11 +3182,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.2782587288286803</v>
+        <v>0.4214242943426267</v>
       </c>
     </row>
     <row r="82">
@@ -3194,19 +3194,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45223</v>
+        <v>45210</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_013</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3216,11 +3216,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.7011871290221805</v>
+        <v>0.6807084204061078</v>
       </c>
     </row>
     <row r="83">
@@ -3228,19 +3228,19 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45223</v>
+        <v>45226</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_007</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(1750.0, 1900.0)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3250,11 +3250,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.4282921431054111</v>
+        <v>0.3491686460807601</v>
       </c>
     </row>
     <row r="84">
@@ -3262,19 +3262,19 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45230</v>
+        <v>45226</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Channel.C_005</t>
+          <t>Channel.C_013</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(250.0, 600.0)</t>
+          <t>(1600.0, 1900.0)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.3662192488461702</v>
+        <v>0.3560878488487055</v>
       </c>
     </row>
     <row r="85">
@@ -3296,32 +3296,1290 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>(1600.0, 1900.0)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0.3909934661242316</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>(1600.0, 1900.0)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0.3967597950074394</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>(1600.0, 1900.0)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0.3729384783715824</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>(200.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0.5230949908029019</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>(200.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0.2949695925005342</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>(200.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0.3123311812374354</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>(200.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0.2780116238025429</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0.6068439833309049</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0.3558488529877364</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0.3126286936786741</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0.3652133205520296</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0.418862309657889</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0.3553765069507296</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0.5205614776791224</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0.2795215205712651</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0.409660941324242</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0.2739757885234303</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Channel.C_006</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>(2200.0, 2300.0)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0.3140816707841142</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>(700.0, 850.0)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0.4332649852960915</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Channel.C_008</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>(900.0, 1050.0)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0.7698733890977872</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Channel.C_024</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>(1450.0, 1750.0)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0.3586400954089719</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Channel.C_024</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>(1450.0, 1750.0)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.5793234171024466</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Channel.C_008</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>(750.0, 850.0)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0.4199608101170635</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C108" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Channel.C_008</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>(750.0, 850.0)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0.4208410158805687</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Channel.C_015_Unit 1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>(2000.0, 2150.0)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.3027352085354026</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0.3395197957935601</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0.2501580879576221</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0.3162297823038918</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0.2887803909777151</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0.4040581760294064</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0.4283440228402101</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0.3806914464845498</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0.251227808839487</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0.2782587288286803</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0.7011871290221805</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0.4282921431054111</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C121" t="n">
         <v>1</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>Channel.C_005</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>(250.0, 600.0)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>AgonismTo</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3662192488461702</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Channel.C_005</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>(250.0, 600.0)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>AgonismTo</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
         <is>
           <t>151J</t>
         </is>
       </c>
-      <c r="H85" t="n">
+      <c r="H122" t="n">
         <v>0.3770346030724412</v>
       </c>
     </row>
